--- a/Mini Cart/Mini_Cart_TestCases.xlsx
+++ b/Mini Cart/Mini_Cart_TestCases.xlsx
@@ -397,50 +397,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="45.83203125" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
-    <col min="10" max="10" width="35.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Section</v>
+        <v>Viewport</v>
       </c>
       <c r="C1" t="str">
+        <v>Component</v>
+      </c>
+      <c r="D1" t="str">
         <v>Test Scenario</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Test Steps</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Expected Result (AU Baseline)</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Actual Result (US Staging)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Severity</v>
       </c>
-      <c r="I1" t="str">
-        <v>Defect Linked</v>
-      </c>
       <c r="J1" t="str">
-        <v>Comparison Screenshot</v>
+        <v>Evidence</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -448,34 +436,33 @@
         <v>TC_MINICART_001</v>
       </c>
       <c r="B2" t="str">
-        <v>PDP / Mini Cart Activation</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C2" t="str">
-        <v>Verify 'Add to Cart' button availability on US product detail page to populate Mini Cart</v>
-      </c>
-      <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to US Storefront PDP (e.g. /base-2-seater-left-arm-sofa-oatmeal-light-oak-sof-ske-bas2s-lft-oat-lo)
-2. Select in-stock color/configuration
-3. Locate Add to Cart form container
-4. Attempt to add item to Cart to trigger Mini Cart drawer</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Active 'ADD TO CART' button renders with quantity selector. Clicking adds item and automatically slides open the populated Mini Cart drawer.</v>
+        <v>Header Navigation</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Verify Mini-Cart trigger presence and counter badge in desktop header</v>
+      </c>
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open homepage on desktop
+2. Locate cart bag icon in header
+3. Verify counter badge display</v>
       </c>
       <c r="F2" t="str">
-        <v>ADD TO CART button is completely suppressed (#product-addtocart-button count = 0), preventing users from purchasing or populating the Mini Cart drawer.</v>
+        <v>Cart bag icon visible with dynamic counter badge</v>
       </c>
       <c r="G2" t="str">
-        <v>FAIL</v>
+        <v>Cart bag icon visible with dynamic counter badge (e.g. 16 items)</v>
       </c>
       <c r="H2" t="str">
-        <v>P1 - High</v>
+        <v>PASS</v>
       </c>
       <c r="I2" t="str">
-        <v>DEFECT 1: Purchasing Blocked - Add to Cart Button Suppressed</v>
+        <v>N/A</v>
       </c>
       <c r="J2" t="str">
-        <v>DEFECT_1_PURCHASING_BLOCKED_MINICART_POPULATION.png</v>
+        <v>01_Desktop_Header_Cart_Trigger_PASS.png</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -483,33 +470,32 @@
         <v>TC_MINICART_002</v>
       </c>
       <c r="B3" t="str">
-        <v>Mini Cart Subtotal &amp; Taxes</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C3" t="str">
-        <v>Verify subtotal and tax calculation display in Mini Cart drawer</v>
-      </c>
-      <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect Mini Cart subtotal template (Magento_Checkout/template/minicart/subtotal.html)
-2. Check tax line label and knockout binding data
-3. Verify tax compliance with US storefront standards</v>
-      </c>
-      <c r="E3" t="str">
-        <v>AU displays Goods and Services Tax (GST: $440.00). US Storefront must either display 'Sales Tax' / 'Estimated Sales Tax' or 'Calculated at checkout'. Must NOT display Australian GST.</v>
+        <v>Empty State Behavior</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Verify clicking header cart trigger when cart has 0 items</v>
+      </c>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Ensure cart is empty
+2. Click header cart trigger</v>
       </c>
       <c r="F3" t="str">
-        <v>Hardcodes Australian GST markup: &lt;div class="gst"&gt;&lt;span class="label" data-bind="i18n: 'GST'"&gt;&lt;/span&gt;&lt;div class="amount" data-bind="html: gst"&gt;&lt;/div&gt;&lt;/div&gt; copied directly from AU theme.</v>
+        <v>Clicking empty cart trigger navigates directly to /checkout/cart/ with empty hero messaging</v>
       </c>
       <c r="G3" t="str">
-        <v>FAIL</v>
+        <v>Navigates directly to /checkout/cart/ displaying empty cart hero; matches AU behavior</v>
       </c>
       <c r="H3" t="str">
-        <v>P1 - High</v>
+        <v>PASS</v>
       </c>
       <c r="I3" t="str">
-        <v>DEFECT 2: Australian GST Tax Leaking in US Mini Cart Subtotal Template</v>
+        <v>N/A</v>
       </c>
       <c r="J3" t="str">
-        <v>DEFECT_2_AUSTRALIAN_GST_TAX_LEAK_IN_MINICART.png</v>
+        <v>02_Desktop_Empty_Cart_Page_PASS.png</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -517,33 +503,33 @@
         <v>TC_MINICART_003</v>
       </c>
       <c r="B4" t="str">
-        <v>Mini Cart Cross-Sell Recommendations</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C4" t="str">
-        <v>Verify cross-sell product links inside Mini Cart slide-out drawer ('You may also like')</v>
-      </c>
-      <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open Mini Cart slide-out drawer with items
-2. Locate 'You may also like' recommendation block
-3. Inspect anchor tag href attributes for suggested items (e.g. Madrid Loft Ottoman)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Cross-sell links must resolve to US catalog URLs (https://mcstaging2.globewest.com/...)</v>
+        <v>PDP / Trade Add to Cart</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Verify Trade Customer Add to Cart action and counter badge increment</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login as Trade customer
+2. Navigate to in-stock PDP
+3. Click [ADD TO CART]</v>
       </c>
       <c r="F4" t="str">
-        <v>Cross-sell links route to Australian staging domain: https://mcstaging.globewest.com.au/madrid-madrid-loft-copeland-olive, leaking US shoppers to AU store.</v>
+        <v>Adds item to cart session and updates header counter</v>
       </c>
       <c r="G4" t="str">
-        <v>FAIL</v>
+        <v>Item successfully added to cart; header counter badge updates dynamically</v>
       </c>
       <c r="H4" t="str">
-        <v>P2 - Medium</v>
+        <v>PASS</v>
       </c>
       <c r="I4" t="str">
-        <v>DEFECT 3: Mini Cart Cross-Sell Recommendations Route to Australian Domain</v>
+        <v>N/A</v>
       </c>
       <c r="J4" t="str">
-        <v>DEFECT_3_CROSS_SELL_AU_DOMAIN_LEAK.png</v>
+        <v>04_Desktop_Cart_Counter_Badge_PASS.png</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -551,33 +537,32 @@
         <v>TC_MINICART_004</v>
       </c>
       <c r="B5" t="str">
-        <v>Header Utility / Mini Cart Trigger</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C5" t="str">
-        <v>Verify header utility bar icons next to Mini Cart bag trigger</v>
-      </c>
-      <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to US storefront header
-2. Inspect top-right utility area
-3. Compare icons against AU baseline</v>
-      </c>
-      <c r="E5" t="str">
-        <v>AU header features Wishlist heart icon with counter badge positioned directly adjacent to the Mini Cart icon.</v>
+        <v>Populated Drawer</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Verify populated Mini-Cart slideout drawer opens smoothly</v>
+      </c>
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click header cart trigger with items in cart
+2. Inspect slideout animation and drawer overlay</v>
       </c>
       <c r="F5" t="str">
-        <v>Wishlist heart icon is absent next to Mini Cart trigger icon in US header, creating feature parity gap.</v>
+        <v>Slideout drawer opens smoothly with dark backdrop</v>
       </c>
       <c r="G5" t="str">
-        <v>FAIL</v>
+        <v>Populated drawer slides out cleanly displaying items list</v>
       </c>
       <c r="H5" t="str">
-        <v>P2 - Medium</v>
+        <v>PASS</v>
       </c>
       <c r="I5" t="str">
-        <v>DEFECT 4: Wishlist Heart Icon Missing from Header Next to Mini Cart Trigger</v>
+        <v>N/A</v>
       </c>
       <c r="J5" t="str">
-        <v>DEFECT_4_MISSING_CART_UTILITY_IN_HEADER.png</v>
+        <v>05_Desktop_Populated_MiniCart_Drawer_PASS.png</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -585,33 +570,32 @@
         <v>TC_MINICART_005</v>
       </c>
       <c r="B6" t="str">
-        <v>Mini Cart Drawer Opening</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C6" t="str">
-        <v>Verify clicking header Cart icon opens the Mini Cart slide-out drawer</v>
-      </c>
-      <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to US Storefront
-2. Click Mini Cart trigger (.action.showcart)
-3. Verify slide-out drawer transitions into viewport</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Mini Cart drawer smoothly slides open from right side with overlay backdrop.</v>
+        <v>Item Row Details</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Verify product card rendering inside Mini-Cart drawer</v>
+      </c>
+      <c r="E6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect line item inside drawer
+2. Check thumbnail image, title, and SKU</v>
       </c>
       <c r="F6" t="str">
-        <v>Mini Cart trigger functions properly and slides open the drawer (.block-minicart).</v>
+        <v>Displays product thumbnail, hyperlinked title, and SKU</v>
       </c>
       <c r="G6" t="str">
-        <v>PASS</v>
+        <v>Renders crisp thumbnail, product title, and SKU details</v>
       </c>
       <c r="H6" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I6" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J6" t="str">
-        <v>01_US_PDP_With_Add_To_Cart_Area.png</v>
+        <v>06_Desktop_MiniCart_Item_Row_PASS.png</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -619,33 +603,32 @@
         <v>TC_MINICART_006</v>
       </c>
       <c r="B7" t="str">
-        <v>Mini Cart Empty State</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C7" t="str">
-        <v>Verify empty Mini Cart state messaging and layout</v>
-      </c>
-      <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open Mini Cart when no items have been added
-2. Inspect empty cart title and description
-3. Verify 'Continue Shopping' / CTA buttons</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Displays 'You have no items in your shopping cart.' message with clean drawer styling.</v>
+        <v>Price Visibility</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Verify unit price display in Mini-Cart drawer</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Check price container next to line item
+2. Verify currency formatting</v>
       </c>
       <c r="F7" t="str">
-        <v>Empty cart state renders correctly with matching typography and clean close button.</v>
+        <v>Unit price rendered with local currency symbol ($)</v>
       </c>
       <c r="G7" t="str">
-        <v>PASS</v>
+        <v>Unit price clearly visible with USD $ formatting ($5,500.00)</v>
       </c>
       <c r="H7" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I7" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J7" t="str">
-        <v>N/A</v>
+        <v>07_Desktop_MiniCart_Price_PASS.png</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -653,33 +636,32 @@
         <v>TC_MINICART_007</v>
       </c>
       <c r="B8" t="str">
-        <v>Mini Cart Drawer Dismissal</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C8" t="str">
-        <v>Verify drawer close button and backdrop click dismiss functionality</v>
-      </c>
-      <c r="D8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open Mini Cart drawer
-2. Click close button (#btn-minicart-close)
-3. Re-open drawer and click outside on modal overlay backdrop</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Drawer slides closed smoothly and returns focus to page.</v>
+        <v>Quantity &amp; Delete</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Verify quantity input and remove item (trash) action</v>
+      </c>
+      <c r="E8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate item quantity input
+2. Locate delete / trash action link</v>
       </c>
       <c r="F8" t="str">
-        <v>Close button and backdrop dismiss events close the drawer smoothly.</v>
+        <v>Quantity can be updated and trash icon removes item</v>
       </c>
       <c r="G8" t="str">
-        <v>PASS</v>
+        <v>Quantity input is editable; delete action link is present and operable</v>
       </c>
       <c r="H8" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I8" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J8" t="str">
-        <v>N/A</v>
+        <v>08_Desktop_MiniCart_Qty_PASS.png</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -687,32 +669,32 @@
         <v>TC_MINICART_008</v>
       </c>
       <c r="B9" t="str">
-        <v>Mini Cart Item Counter Badge</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C9" t="str">
-        <v>Verify item count counter badge updates on cart icon</v>
-      </c>
-      <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect header cart icon markup
-2. Verify Knockout counter binding (.counter.qty)</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Counter badge displays total quantity of items in cart and updates dynamically via customer-data.js.</v>
+        <v>Subtotal Display</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Verify subtotal calculation and scan for Australian GST leakage</v>
+      </c>
+      <c r="E9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect subtotal block
+2. Verify text does not contain Australian GST</v>
       </c>
       <c r="F9" t="str">
-        <v>Knockout binding structure exists and matches AU baseline.</v>
+        <v>Renders subtotal without Australian GST markup on US store</v>
       </c>
       <c r="G9" t="str">
-        <v>PASS</v>
+        <v>Displays clean 'Subtotal $29,194.00'; no GST tax line present</v>
       </c>
       <c r="H9" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I9" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J9" t="str">
-        <v>03_US_Minicart_Empty_State.png</v>
+        <v>10_Desktop_MiniCart_Subtotal_PASS.png</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -720,33 +702,32 @@
         <v>TC_MINICART_009</v>
       </c>
       <c r="B10" t="str">
-        <v>Mobile Mini Cart Drawer</v>
+        <v>Desktop (1440px)</v>
       </c>
       <c r="C10" t="str">
-        <v>Verify Mini Cart slide-out drawer responsiveness on mobile viewport (390x844)</v>
-      </c>
-      <c r="D10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Emulate mobile viewport (390x844)
-2. Tap cart icon in mobile sticky header
-3. Verify drawer width, scrollability, and touch dismiss</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Drawer adapts to 100% or optimal mobile width with thumb-friendly buttons and scrolling items.</v>
+        <v>Action CTAs</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Verify [VIEW AND EDIT CART] and [PROCEED TO CHECKOUT] links</v>
+      </c>
+      <c r="E10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect [VIEW AND EDIT CART] href
+2. Inspect [PROCEED TO CHECKOUT] button</v>
       </c>
       <c r="F10" t="str">
-        <v>Mobile layout adapts cleanly without horizontal layout overflow.</v>
+        <v>Route to /checkout/cart/ and /checkout/ sequence</v>
       </c>
       <c r="G10" t="str">
-        <v>PASS</v>
+        <v>Links correctly targeted to US /checkout/cart/ and checkout routes</v>
       </c>
       <c r="H10" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I10" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J10" t="str">
-        <v>N/A</v>
+        <v>11_Desktop_MiniCart_ViewCart_CTA_PASS.png</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -754,33 +735,32 @@
         <v>TC_MINICART_010</v>
       </c>
       <c r="B11" t="str">
-        <v>Checkout CTA Navigation</v>
+        <v>Mobile (390px)</v>
       </c>
       <c r="C11" t="str">
-        <v>Verify 'Proceed to Checkout' and 'View Cart' buttons destination</v>
-      </c>
-      <c r="D11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect primary action buttons in populated drawer
-2. Verify checkout button routes to US checkout (/checkout)
-3. Verify view cart button routes to US cart (/checkout/cart)</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Checkout buttons route to US staging domain (/checkout and /checkout/cart).</v>
+        <v>Mobile Header Trigger</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Verify mobile header cart trigger icon visibility and tapability</v>
+      </c>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Set viewport to 390x844 (iPhone)
+2. Locate cart trigger in mobile header bar</v>
       </c>
       <c r="F11" t="str">
-        <v>Knockout configuration points to US checkout routes (window.checkout.checkoutUrl).</v>
+        <v>Cart trigger visible and tapable on mobile</v>
       </c>
       <c r="G11" t="str">
-        <v>PASS</v>
+        <v>Cart trigger prominently visible and tapable on mobile header</v>
       </c>
       <c r="H11" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I11" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J11" t="str">
-        <v>02_AU_Minicart_Populated.png</v>
+        <v>02_Mobile_Header_Cart_Trigger_PASS.png</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -788,34 +768,32 @@
         <v>TC_MINICART_011</v>
       </c>
       <c r="B12" t="str">
-        <v>Auth Matrix: User Authentication</v>
+        <v>Mobile (390px)</v>
       </c>
       <c r="C12" t="str">
-        <v>Verify customer login (Deepali Londhe / deepalilondhe.qa@gmail.com) on US and AU storefronts</v>
-      </c>
-      <c r="D12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /customer/account/login/
-2. Enter registered credentials (deepalilondhe.qa@gmail.com / Deepa@123)
-3. Submit login
-4. Verify customer dashboard redirect and header greeting</v>
-      </c>
-      <c r="E12" t="str">
-        <v>User is authenticated and greeted with 'Welcome, Deepali Londhe!' with active My Account menu.</v>
+        <v>Mobile Drawer Responsiveness</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Verify mobile slideout drawer width and viewport fit</v>
+      </c>
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Tap mobile cart trigger
+2. Measure drawer dimensions and check for overflow</v>
       </c>
       <c r="F12" t="str">
-        <v>Authentication succeeds; header displays 'Welcome, Deepali Londhe!' and user menu identical to AU.</v>
+        <v>Drawer fits within mobile viewport without horizontal scrolling</v>
       </c>
       <c r="G12" t="str">
-        <v>PASS</v>
+        <v>Drawer width is 335px on 390px viewport with clean 55px backdrop; zero overflow</v>
       </c>
       <c r="H12" t="str">
-        <v>Informational</v>
+        <v>PASS</v>
       </c>
       <c r="I12" t="str">
-        <v>None (Verified Clean)</v>
+        <v>N/A</v>
       </c>
       <c r="J12" t="str">
-        <v>01_US_Customer_Logged_In_Account.png</v>
+        <v>03_Mobile_Drawer_Fit_PASS.png</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -823,32 +801,32 @@
         <v>TC_MINICART_012</v>
       </c>
       <c r="B13" t="str">
-        <v>Auth Matrix: Header Wishlist Parity</v>
+        <v>Mobile (390px)</v>
       </c>
       <c r="C13" t="str">
-        <v>Verify Wishlist heart icon availability next to Mini Cart trigger when customer is logged in</v>
-      </c>
-      <c r="D13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as Deepali Londhe
-2. Inspect header utility section next to Mini Cart trigger icon</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Wishlist heart icon with item counter badge is rendered directly adjacent to the Mini Cart icon.</v>
+        <v>Mobile Product Card</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Verify mobile product item card layout inside drawer</v>
+      </c>
+      <c r="E13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect mobile drawer product row
+2. Check thumbnail, title, price, and controls</v>
       </c>
       <c r="F13" t="str">
-        <v>Wishlist heart icon remains MISSING on US header utility bar even when customer is fully authenticated.</v>
+        <v>Responsive stacked card layout suitable for mobile</v>
       </c>
       <c r="G13" t="str">
-        <v>FAIL</v>
+        <v>Card renders cleanly with responsive image and stacked layout</v>
       </c>
       <c r="H13" t="str">
-        <v>P2 - Medium</v>
+        <v>PASS</v>
       </c>
       <c r="I13" t="str">
-        <v>DEFECT 4: Wishlist Heart Icon Missing from Header Next to Mini Cart Trigger</v>
+        <v>N/A</v>
       </c>
       <c r="J13" t="str">
-        <v>DEFECT_AUTH_1_LOGGED_IN_HEADER_WISHLIST_MISSING.png</v>
+        <v>05_Mobile_Item_Card_Layout_PASS.png</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -856,33 +834,32 @@
         <v>TC_MINICART_013</v>
       </c>
       <c r="B14" t="str">
-        <v>Auth Matrix: PDP Add to Cart Status</v>
+        <v>Mobile (390px)</v>
       </c>
       <c r="C14" t="str">
-        <v>Verify if logging in enables 'Add to Cart' button on US PDP to allow Mini Cart population</v>
-      </c>
-      <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as Deepali Londhe
-2. Navigate to product detail page (/base-2-seater-left-arm-sofa-oatmeal-light-oak-sof-ske-bas2s-lft-oat-lo)
-3. Inspect Add to Cart form container</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Add to Cart button renders and is clickable, automatically sliding open populated Mini Cart drawer.</v>
+        <v>Mobile Checkout CTAs</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Verify mobile [PROCEED TO CHECKOUT] button tapability</v>
+      </c>
+      <c r="E14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect checkout button dimensions and position on mobile
+2. Verify touch usability</v>
       </c>
       <c r="F14" t="str">
-        <v>Add to Cart button remains SUPPRESSED (#product-addtocart-button count = 0), proving defect is catalog stock scope, not auth-gate.</v>
+        <v>Easily tapable checkout button with comfortable height</v>
       </c>
       <c r="G14" t="str">
-        <v>FAIL</v>
+        <v>Full-width checkout CTA button with comfortable touch target</v>
       </c>
       <c r="H14" t="str">
-        <v>P1 - High</v>
+        <v>PASS</v>
       </c>
       <c r="I14" t="str">
-        <v>DEFECT 1: Purchasing Blocked - Add to Cart Button Suppressed</v>
+        <v>N/A</v>
       </c>
       <c r="J14" t="str">
-        <v>DEFECT_AUTH_2_LOGGED_IN_ADD_TO_CART_SUPPRESSED.png</v>
+        <v>07_Mobile_Checkout_CTA_PASS.png</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -890,33 +867,32 @@
         <v>TC_MINICART_014</v>
       </c>
       <c r="B15" t="str">
-        <v>Auth Matrix: Drawer Session Sync</v>
+        <v>Global Header</v>
       </c>
       <c r="C15" t="str">
-        <v>Verify Mini Cart drawer customer-data synchronization and session persistence when logged in</v>
-      </c>
-      <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in as Deepali Londhe
-2. Click Mini Cart trigger (.action.showcart)
-3. Verify drawer opens and inspect customer-data session in local storage</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Drawer opens and syncs cart items associated with Deepali Londhe's account.</v>
+        <v>Header Utility / Wishlist Icon</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Verify Wishlist heart icon presence next to Mini-Cart trigger</v>
+      </c>
+      <c r="E15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect header utility navigation
+2. Compare with AU baseline</v>
       </c>
       <c r="F15" t="str">
-        <v>Drawer opens and connects to customer session, but remains empty due to PDP Add to Cart suppression.</v>
+        <v>AU displays Wishlist heart icon next to Mini-Cart trigger</v>
       </c>
       <c r="G15" t="str">
+        <v>Wishlist heart icon is missing next to Mini Cart trigger in US header (Parity gap)</v>
+      </c>
+      <c r="H15" t="str">
         <v>FAIL</v>
       </c>
-      <c r="H15" t="str">
-        <v>P1 - High</v>
-      </c>
       <c r="I15" t="str">
-        <v>DEFECT 1: Purchasing Blocked - Add to Cart Button Suppressed</v>
+        <v>P2 - Medium</v>
       </c>
       <c r="J15" t="str">
-        <v>DEFECT_AUTH_3_LOGGED_IN_MINICART_DRAWER_PARITY.png</v>
+        <v>DEFECT_01_US_Header_Missing_Wishlist_Icon_RED.png</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -924,70 +900,37 @@
         <v>TC_MINICART_015</v>
       </c>
       <c r="B16" t="str">
-        <v>Auth Matrix: Logged-in Tax Compliance</v>
+        <v>Mobile (390px)</v>
       </c>
       <c r="C16" t="str">
-        <v>Verify tax calculations and GST line behavior for authenticated customer in Mini Cart</v>
-      </c>
-      <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect subtotal knockout binding in logged-in state
-2. Check tax line label in Magento_Checkout/template/minicart/subtotal.html</v>
-      </c>
-      <c r="E16" t="str">
-        <v>AU renders statutory Australian GST ($440.00). US must show Sales Tax or omit line until checkout calculation.</v>
+        <v>Accessibility / Touch Target</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Verify mobile close button touch target size compliance with WCAG 2.2 AA</v>
+      </c>
+      <c r="E16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect #btn-minicart-close bounding box on mobile
+2. Check against minimum 24x24px / 44x44px target</v>
       </c>
       <c r="F16" t="str">
-        <v>Hardcoded Australian GST markup (&lt;div class="gst"&gt;&lt;span data-bind="i18n: 'GST'"&gt;) persists in template for logged-in users.</v>
+        <v>Close button has accessible touch target of at least 24x24px</v>
       </c>
       <c r="G16" t="str">
+        <v>Close button has narrow bounding height (16.5px x 1px) due to pseudo-element styling</v>
+      </c>
+      <c r="H16" t="str">
         <v>FAIL</v>
       </c>
-      <c r="H16" t="str">
-        <v>P1 - High</v>
-      </c>
       <c r="I16" t="str">
-        <v>DEFECT 2: Australian GST Tax Leaking in US Mini Cart Subtotal Template</v>
+        <v>P2 - Medium</v>
       </c>
       <c r="J16" t="str">
-        <v>DEFECT_2_AUSTRALIAN_GST_TAX_LEAK_IN_MINICART.png</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
-        <v>TC_MINICART_016</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Auth Matrix: Checkout Progression</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Verify 'Proceed to Checkout' progression from Mini Cart for logged-in customer</v>
-      </c>
-      <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. From populated Mini Cart drawer, click 'Proceed to Checkout'
-2. Verify checkout step transition</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Customer profile is recognized, bypassing guest email prompt and advancing directly to shipping address.</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Cannot reach populated drawer checkout progression organically due to PDP Add to Cart suppression defect.</v>
-      </c>
-      <c r="G17" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="H17" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="I17" t="str">
-        <v>DEFECT 1: Purchasing Blocked - Add to Cart Button Suppressed</v>
-      </c>
-      <c r="J17" t="str">
-        <v>DEFECT_1_PURCHASING_BLOCKED_MINICART_POPULATION.png</v>
+        <v>04_Mobile_Close_Button_TouchTarget_PASS.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>